--- a/data/未來PE報表.xlsx
+++ b/data/未來PE報表.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="主表_按PEG排序" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="A_B級_按PEG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="🟢雙低(最佳)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="🔵成長卡位" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="⚠️便宜陷阱" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="🔴真貴" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="循環股(看PBR非PE)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="統計" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主表_按PEG排序" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_B級_按PEG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🟢雙低(最佳)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔵成長卡位" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️便宜陷阱" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔴真貴" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="循環股(看PBR非PE)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="統計" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,13 +24,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,92 +436,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -6210,92 +6222,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -10258,92 +10270,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -10976,92 +10988,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -11624,92 +11636,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -12138,92 +12150,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -13734,37 +13746,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -18609,12 +18621,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>

--- a/data/未來PE報表.xlsx
+++ b/data/未來PE報表.xlsx
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
         <v>24.1</v>
@@ -904,13 +904,13 @@
         <v>16.72</v>
       </c>
       <c r="J7" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="K7" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2462,13 +2462,13 @@
         <v>7.89</v>
       </c>
       <c r="J30" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -3642,115 +3642,113 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>⚠️成長耗盡</t>
+          <t>🔴真貴</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>20.2</v>
+        <v>36.5</v>
       </c>
       <c r="G48" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I48" t="n">
-        <v>34.6</v>
+        <v>7.93</v>
       </c>
       <c r="J48" t="n">
-        <v>18.4</v>
+        <v>30.9</v>
       </c>
       <c r="K48" t="n">
-        <v>18.4</v>
+        <v>33.6</v>
       </c>
       <c r="L48" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>52.4</v>
+        <v>9.4</v>
       </c>
       <c r="P48" t="n">
-        <v>1.91</v>
+        <v>0.49</v>
       </c>
       <c r="Q48" t="n">
-        <v>19.2</v>
+        <v>8.4</v>
       </c>
       <c r="R48" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>65</v>
-      </c>
+          <t>金融🏦</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>🔴真貴</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>36.5</v>
+        <v>19.8</v>
       </c>
       <c r="G49" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H49" t="n">
-        <v>18</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>7.93</v>
+        <v>1.66</v>
       </c>
       <c r="J49" t="n">
-        <v>30.9</v>
+        <v>22.7</v>
       </c>
       <c r="K49" t="n">
-        <v>33.6</v>
+        <v>22.7</v>
       </c>
       <c r="L49" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3763,80 +3761,82 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
-        <v>8.4</v>
+        <v>58.3</v>
       </c>
       <c r="R49" t="n">
-        <v>18</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>金融🏦</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>92</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>🔴真貴</t>
+          <t>⚠️成長耗盡</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>19.8</v>
+        <v>20.9</v>
       </c>
       <c r="G50" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="H50" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I50" t="n">
-        <v>1.66</v>
+        <v>34.6</v>
       </c>
       <c r="J50" t="n">
-        <v>22.7</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>22.7</v>
+        <v>19</v>
       </c>
       <c r="L50" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
+        <v>52.4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.91</v>
+      </c>
       <c r="Q50" t="n">
-        <v>58.3</v>
+        <v>19.2</v>
       </c>
       <c r="R50" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H72" t="n">
         <v>2.8</v>
@@ -5302,17 +5302,17 @@
         <v>11.26</v>
       </c>
       <c r="J72" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="K72" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="L72" t="n">
-        <v>7.41</v>
+        <v>7.46</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6598,10 +6598,10 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="G93" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
@@ -11126,12 +11126,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -11148,10 +11148,10 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>25.3</v>
+        <v>142.3</v>
       </c>
       <c r="G172" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
@@ -11160,7 +11160,7 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -11169,27 +11169,27 @@
         </is>
       </c>
       <c r="O172" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="P172" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="Q172" t="n">
-        <v>11.2</v>
+        <v>32.4</v>
       </c>
       <c r="R172" t="n">
-        <v>-10.3</v>
+        <v>-25.4</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台灣精銳</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11206,10 +11206,10 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>142.3</v>
+        <v>55.3</v>
       </c>
       <c r="G173" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
@@ -11218,7 +11218,7 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -11227,27 +11227,27 @@
         </is>
       </c>
       <c r="O173" t="n">
-        <v>10.3</v>
+        <v>9.4</v>
       </c>
       <c r="P173" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="Q173" t="n">
-        <v>32.4</v>
+        <v>6.9</v>
       </c>
       <c r="R173" t="n">
-        <v>-25.4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>台灣精銳</t>
+          <t>尚凡*</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>55.3</v>
+        <v>25</v>
       </c>
       <c r="G174" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -11276,7 +11276,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -11285,27 +11285,27 @@
         </is>
       </c>
       <c r="O174" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="P174" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="Q174" t="n">
-        <v>6.9</v>
+        <v>15</v>
       </c>
       <c r="R174" t="n">
-        <v>4.9</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>尚凡*</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G175" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -11343,27 +11343,27 @@
         </is>
       </c>
       <c r="O175" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="P175" t="n">
-        <v>1.01</v>
+        <v>6.49</v>
       </c>
       <c r="Q175" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="R175" t="n">
-        <v>-72</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>豐達科</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11380,10 +11380,10 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>23.3</v>
+        <v>2.6</v>
       </c>
       <c r="G176" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -11392,7 +11392,7 @@
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -11401,27 +11401,25 @@
         </is>
       </c>
       <c r="O176" t="n">
-        <v>9.4</v>
+        <v>37.9</v>
       </c>
       <c r="P176" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="Q176" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="R176" t="n">
-        <v>0.8</v>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>豐達科</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11438,10 +11436,10 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>2.6</v>
+        <v>23.3</v>
       </c>
       <c r="G177" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
@@ -11450,7 +11448,7 @@
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -11459,15 +11457,17 @@
         </is>
       </c>
       <c r="O177" t="n">
-        <v>37.9</v>
+        <v>9.4</v>
       </c>
       <c r="P177" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="Q177" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="R177" t="inlineStr"/>
+        <v>56.2</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11530,12 +11530,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11544,7 +11544,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -11552,10 +11552,10 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>27</v>
+        <v>12.7</v>
       </c>
       <c r="G179" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -11564,36 +11564,34 @@
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 無成長率</t>
         </is>
       </c>
       <c r="O179" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="P179" t="n">
-        <v>6.49</v>
+        <v>-0.39</v>
       </c>
       <c r="Q179" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="R179" t="n">
-        <v>2.6</v>
-      </c>
+        <v>-72.7</v>
+      </c>
+      <c r="R179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>和亞智慧</t>
+          <t>緯軟</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11610,10 +11608,10 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="G180" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
@@ -11622,34 +11620,36 @@
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>⏸ 無成長率</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O180" t="n">
-        <v>32</v>
+        <v>15.9</v>
       </c>
       <c r="P180" t="n">
-        <v>-0.39</v>
+        <v>0.53</v>
       </c>
       <c r="Q180" t="n">
-        <v>-72.7</v>
-      </c>
-      <c r="R180" t="inlineStr"/>
+        <v>29.2</v>
+      </c>
+      <c r="R180" t="n">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>緯軟</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>14.3</v>
+        <v>25.6</v>
       </c>
       <c r="G181" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -11678,7 +11678,7 @@
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -11687,16 +11687,16 @@
         </is>
       </c>
       <c r="O181" t="n">
-        <v>15.9</v>
+        <v>9.5</v>
       </c>
       <c r="P181" t="n">
-        <v>0.53</v>
+        <v>2.12</v>
       </c>
       <c r="Q181" t="n">
-        <v>29.2</v>
+        <v>11.2</v>
       </c>
       <c r="R181" t="n">
-        <v>-0.2</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="182">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
         <v>24.1</v>
@@ -15878,13 +15878,13 @@
         <v>16.72</v>
       </c>
       <c r="J6" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="K6" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -17168,13 +17168,13 @@
         <v>7.89</v>
       </c>
       <c r="J25" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -18018,137 +18018,137 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>⚠️成長耗盡</t>
+          <t>🔴真貴</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>20.2</v>
+        <v>36.5</v>
       </c>
       <c r="G38" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I38" t="n">
-        <v>34.6</v>
+        <v>7.93</v>
       </c>
       <c r="J38" t="n">
-        <v>18.4</v>
+        <v>30.9</v>
       </c>
       <c r="K38" t="n">
-        <v>18.4</v>
+        <v>33.6</v>
       </c>
       <c r="L38" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>52.4</v>
+        <v>9.4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>0.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>19.2</v>
+        <v>8.4</v>
       </c>
       <c r="R38" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>🔴真貴</t>
+          <t>⚠️成長耗盡</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>36.5</v>
+        <v>20.9</v>
       </c>
       <c r="G39" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="H39" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I39" t="n">
-        <v>7.93</v>
+        <v>34.6</v>
       </c>
       <c r="J39" t="n">
-        <v>30.9</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>33.6</v>
+        <v>19</v>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>9.4</v>
+        <v>52.4</v>
       </c>
       <c r="P39" t="n">
-        <v>0.49</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.4</v>
+        <v>19.2</v>
       </c>
       <c r="R39" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="G71" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -21688,10 +21688,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
         <v>24.1</v>
@@ -21700,13 +21700,13 @@
         <v>16.72</v>
       </c>
       <c r="J5" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="K5" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -23122,10 +23122,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>2.8</v>
@@ -23134,17 +23134,17 @@
         <v>11.26</v>
       </c>
       <c r="J6" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>7.41</v>
+        <v>7.46</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -26239,62 +26239,62 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>26.9</v>
+        <v>12.2</v>
       </c>
       <c r="E46" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="F46" t="n">
         <v>63</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.3</v>
+        <v>26.9</v>
       </c>
       <c r="E47" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="F47" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
@@ -26549,24 +26549,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="E56" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F56" t="n">
         <v>73</v>
@@ -26580,12 +26580,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -26594,13 +26594,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>65.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F57" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -26611,89 +26611,89 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>64.40000000000001</v>
+        <v>44.3</v>
       </c>
       <c r="E58" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="F58" t="n">
         <v>74</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>精確</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>44.3</v>
+        <v>69.3</v>
       </c>
       <c r="E59" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F59" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>精確</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>69.3</v>
+        <v>25.6</v>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F60" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>

--- a/data/未來PE報表.xlsx
+++ b/data/未來PE報表.xlsx
@@ -4258,12 +4258,10 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>37</v>
-      </c>
+          <t>金融🏦</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>⚠️成長耗盡</t>
@@ -6150,12 +6148,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6172,10 +6170,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>66.5</v>
+        <v>24</v>
       </c>
       <c r="G85" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -6193,27 +6191,27 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>34.3</v>
+        <v>29.3</v>
       </c>
       <c r="P85" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Q85" t="n">
-        <v>172.1</v>
+        <v>25</v>
       </c>
       <c r="R85" t="n">
-        <v>90.7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6230,10 +6228,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>77.09999999999999</v>
+        <v>163.5</v>
       </c>
       <c r="G86" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -6251,27 +6249,27 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>29.3</v>
+        <v>74.7</v>
       </c>
       <c r="P86" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Q86" t="n">
-        <v>116</v>
+        <v>68.7</v>
       </c>
       <c r="R86" t="n">
-        <v>204.6</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6288,10 +6286,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>163.5</v>
+        <v>66.5</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -6309,27 +6307,27 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>74.7</v>
+        <v>34.3</v>
       </c>
       <c r="P87" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>68.7</v>
+        <v>172.1</v>
       </c>
       <c r="R87" t="n">
-        <v>97.40000000000001</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6346,10 +6344,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>24</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -6370,13 +6368,13 @@
         <v>29.3</v>
       </c>
       <c r="P88" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Q88" t="n">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="R88" t="n">
-        <v>49</v>
+        <v>204.6</v>
       </c>
     </row>
     <row r="89">
@@ -6788,12 +6786,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6810,10 +6808,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>12.2</v>
+        <v>27.9</v>
       </c>
       <c r="G96" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
@@ -6822,7 +6820,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -6831,27 +6829,27 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>20</v>
+        <v>28.8</v>
       </c>
       <c r="P96" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Q96" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="R96" t="n">
-        <v>16.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6868,10 +6866,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>27.9</v>
+        <v>12.2</v>
       </c>
       <c r="G97" t="n">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
@@ -6880,7 +6878,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -6889,27 +6887,27 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>28.8</v>
+        <v>20</v>
       </c>
       <c r="P97" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Q97" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="R97" t="n">
-        <v>36.5</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6926,10 +6924,10 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>72.7</v>
+        <v>45.8</v>
       </c>
       <c r="G98" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
@@ -6947,27 +6945,27 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>48.1</v>
+        <v>14.4</v>
       </c>
       <c r="P98" t="n">
-        <v>0.31</v>
+        <v>1.62</v>
       </c>
       <c r="Q98" t="n">
-        <v>133.1</v>
+        <v>13</v>
       </c>
       <c r="R98" t="n">
-        <v>71.09999999999999</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6984,10 +6982,10 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>45.8</v>
+        <v>72.7</v>
       </c>
       <c r="G99" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
@@ -7005,16 +7003,16 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>14.4</v>
+        <v>48.1</v>
       </c>
       <c r="P99" t="n">
-        <v>1.62</v>
+        <v>0.31</v>
       </c>
       <c r="Q99" t="n">
-        <v>13</v>
+        <v>133.1</v>
       </c>
       <c r="R99" t="n">
-        <v>25.5</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -7484,12 +7482,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>王品</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7506,10 +7504,10 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>310.9</v>
+        <v>14.8</v>
       </c>
       <c r="G108" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
@@ -7518,7 +7516,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -7527,25 +7525,27 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>16.6</v>
+        <v>33.6</v>
       </c>
       <c r="P108" t="n">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="Q108" t="n">
-        <v>118.8</v>
-      </c>
-      <c r="R108" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="R108" t="n">
+        <v>-4.8</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>王品</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7562,10 +7562,10 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>14.8</v>
+        <v>310.9</v>
       </c>
       <c r="G109" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -7583,27 +7583,25 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>33.6</v>
+        <v>16.6</v>
       </c>
       <c r="P109" t="n">
-        <v>2.56</v>
+        <v>1.13</v>
       </c>
       <c r="Q109" t="n">
-        <v>15</v>
-      </c>
-      <c r="R109" t="n">
-        <v>-4.8</v>
-      </c>
+        <v>118.8</v>
+      </c>
+      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7620,10 +7618,10 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>25.5</v>
+        <v>10.5</v>
       </c>
       <c r="G110" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
@@ -7632,7 +7630,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -7641,16 +7639,16 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>17.9</v>
+        <v>41.3</v>
       </c>
       <c r="P110" t="n">
-        <v>1.71</v>
+        <v>-1.31</v>
       </c>
       <c r="Q110" t="n">
-        <v>19</v>
+        <v>224.4</v>
       </c>
       <c r="R110" t="n">
-        <v>15.6</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="111">
@@ -7714,12 +7712,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7736,10 +7734,10 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
       <c r="G112" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
@@ -7748,7 +7746,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -7757,27 +7755,27 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>41.3</v>
+        <v>17.9</v>
       </c>
       <c r="P112" t="n">
-        <v>-1.31</v>
+        <v>1.71</v>
       </c>
       <c r="Q112" t="n">
-        <v>224.4</v>
+        <v>19</v>
       </c>
       <c r="R112" t="n">
-        <v>21.9</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7794,7 +7792,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>62.1</v>
+        <v>36.3</v>
       </c>
       <c r="G113" t="n">
         <v>100</v>
@@ -7815,27 +7813,27 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>12.8</v>
+        <v>14.6</v>
       </c>
       <c r="P113" t="n">
-        <v>3.26</v>
+        <v>1.81</v>
       </c>
       <c r="Q113" t="n">
-        <v>28.6</v>
+        <v>23.7</v>
       </c>
       <c r="R113" t="n">
-        <v>12.6</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7852,7 +7850,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>36.3</v>
+        <v>62.1</v>
       </c>
       <c r="G114" t="n">
         <v>100</v>
@@ -7873,16 +7871,16 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>14.6</v>
+        <v>12.8</v>
       </c>
       <c r="P114" t="n">
-        <v>1.81</v>
+        <v>3.26</v>
       </c>
       <c r="Q114" t="n">
-        <v>23.7</v>
+        <v>28.6</v>
       </c>
       <c r="R114" t="n">
-        <v>27.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="115">
@@ -8174,12 +8172,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>歐買尬</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8196,10 +8194,10 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>17.6</v>
+        <v>165.8</v>
       </c>
       <c r="G120" t="n">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
@@ -8208,7 +8206,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8217,17 +8215,15 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>15.9</v>
+        <v>10.7</v>
       </c>
       <c r="P120" t="n">
-        <v>0.53</v>
+        <v>1.73</v>
       </c>
       <c r="Q120" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="R120" t="n">
-        <v>63.5</v>
-      </c>
+        <v>49.9</v>
+      </c>
+      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8290,12 +8286,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>歐買尬</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8312,10 +8308,10 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>165.8</v>
+        <v>17.6</v>
       </c>
       <c r="G122" t="n">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
@@ -8324,7 +8320,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -8333,15 +8329,17 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>10.7</v>
+        <v>15.9</v>
       </c>
       <c r="P122" t="n">
-        <v>1.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q122" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="R122" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="R122" t="n">
+        <v>63.5</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8404,12 +8402,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>和淞</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8426,10 +8424,10 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>7.3</v>
+        <v>24.5</v>
       </c>
       <c r="G124" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
@@ -8438,34 +8436,36 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>⏸ 無成長率</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>54.1</v>
+        <v>30.7</v>
       </c>
       <c r="P124" t="n">
-        <v>2.21</v>
+        <v>-0.6</v>
       </c>
       <c r="Q124" t="n">
-        <v>2</v>
-      </c>
-      <c r="R124" t="inlineStr"/>
+        <v>301.2</v>
+      </c>
+      <c r="R124" t="n">
+        <v>50.9</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G125" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
@@ -8499,31 +8499,31 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-6%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>12.9</v>
+        <v>48.8</v>
       </c>
       <c r="P125" t="n">
-        <v>1.67</v>
+        <v>-0.36</v>
       </c>
       <c r="Q125" t="n">
-        <v>22.1</v>
+        <v>640.8</v>
       </c>
       <c r="R125" t="n">
-        <v>-5.7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="G126" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
@@ -8552,7 +8552,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -8561,27 +8561,27 @@
         </is>
       </c>
       <c r="O126" t="n">
-        <v>30.7</v>
+        <v>2.8</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.6</v>
+        <v>4.71</v>
       </c>
       <c r="Q126" t="n">
-        <v>301.2</v>
+        <v>-2.6</v>
       </c>
       <c r="R126" t="n">
-        <v>50.9</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8598,10 +8598,10 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>45.2</v>
+        <v>34</v>
       </c>
       <c r="G127" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
@@ -8615,29 +8615,31 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-6%)</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>17.9</v>
+        <v>12.9</v>
       </c>
       <c r="P127" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q127" t="n">
-        <v>730.1</v>
-      </c>
-      <c r="R127" t="inlineStr"/>
+        <v>22.1</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-5.7</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8654,10 +8656,10 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>24.2</v>
+        <v>45.2</v>
       </c>
       <c r="G128" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
@@ -8666,7 +8668,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -8675,27 +8677,25 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>2.8</v>
+        <v>17.9</v>
       </c>
       <c r="P128" t="n">
-        <v>4.71</v>
+        <v>1.5</v>
       </c>
       <c r="Q128" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="R128" t="n">
-        <v>130.9</v>
-      </c>
+        <v>730.1</v>
+      </c>
+      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>和淞</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>26</v>
+        <v>7.3</v>
       </c>
       <c r="G129" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
@@ -8724,36 +8724,34 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 無成長率</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>48.8</v>
+        <v>54.1</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.36</v>
+        <v>2.21</v>
       </c>
       <c r="Q129" t="n">
-        <v>640.8</v>
-      </c>
-      <c r="R129" t="n">
-        <v>29</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8770,10 +8768,10 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>222.9</v>
+        <v>32.2</v>
       </c>
       <c r="G130" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
@@ -8782,7 +8780,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -8791,15 +8789,17 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>6.9</v>
+        <v>31.7</v>
       </c>
       <c r="P130" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="Q130" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="R130" t="inlineStr"/>
+        <v>21.9</v>
+      </c>
+      <c r="R130" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8862,12 +8862,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>32.2</v>
+        <v>222.9</v>
       </c>
       <c r="G132" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
@@ -8896,7 +8896,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -8905,17 +8905,15 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>31.7</v>
+        <v>6.9</v>
       </c>
       <c r="P132" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q132" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R132" t="n">
-        <v>27</v>
-      </c>
+        <v>54.4</v>
+      </c>
+      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8978,12 +8976,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>健喬</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9000,10 +8998,10 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>25.9</v>
+        <v>19.2</v>
       </c>
       <c r="G134" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
@@ -9012,7 +9010,7 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9021,16 +9019,16 @@
         </is>
       </c>
       <c r="O134" t="n">
-        <v>20.2</v>
+        <v>5.9</v>
       </c>
       <c r="P134" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="Q134" t="n">
-        <v>81.7</v>
+        <v>12.9</v>
       </c>
       <c r="R134" t="n">
-        <v>-5.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="135">
@@ -9094,12 +9092,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>健喬</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9116,10 +9114,10 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>19.2</v>
+        <v>35.8</v>
       </c>
       <c r="G136" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
@@ -9128,7 +9126,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -9137,27 +9135,27 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>5.9</v>
+        <v>10.7</v>
       </c>
       <c r="P136" t="n">
-        <v>0.76</v>
+        <v>1.85</v>
       </c>
       <c r="Q136" t="n">
-        <v>12.9</v>
+        <v>37</v>
       </c>
       <c r="R136" t="n">
-        <v>0.6</v>
+        <v>186.3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9174,10 +9172,10 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>35.8</v>
+        <v>25.9</v>
       </c>
       <c r="G137" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
@@ -9186,7 +9184,7 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9195,27 +9193,27 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>10.7</v>
+        <v>20.2</v>
       </c>
       <c r="P137" t="n">
-        <v>1.85</v>
+        <v>0.92</v>
       </c>
       <c r="Q137" t="n">
-        <v>37</v>
+        <v>81.7</v>
       </c>
       <c r="R137" t="n">
-        <v>186.3</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>明基醫</t>
+          <t>寶島科</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9232,10 +9230,10 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>24.7</v>
+        <v>16.6</v>
       </c>
       <c r="G138" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
@@ -9244,7 +9242,7 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -9253,27 +9251,27 @@
         </is>
       </c>
       <c r="O138" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="P138" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q138" t="n">
-        <v>1.2</v>
+        <v>17.4</v>
       </c>
       <c r="R138" t="n">
-        <v>-17.5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>寶島科</t>
+          <t>明基醫</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9290,10 +9288,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>16.6</v>
+        <v>24.7</v>
       </c>
       <c r="G139" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
@@ -9302,7 +9300,7 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -9311,27 +9309,27 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P139" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q139" t="n">
-        <v>17.4</v>
+        <v>1.2</v>
       </c>
       <c r="R139" t="n">
-        <v>-4</v>
+        <v>-17.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>台耀</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9348,10 +9346,10 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>19.4</v>
+        <v>18.5</v>
       </c>
       <c r="G140" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
@@ -9369,27 +9367,27 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="P140" t="n">
-        <v>1.85</v>
+        <v>3.32</v>
       </c>
       <c r="Q140" t="n">
-        <v>26.9</v>
+        <v>-4.9</v>
       </c>
       <c r="R140" t="n">
-        <v>-32.8</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9406,10 +9404,10 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>18.5</v>
+        <v>19.4</v>
       </c>
       <c r="G141" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
@@ -9427,16 +9425,16 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="P141" t="n">
-        <v>3.32</v>
+        <v>1.85</v>
       </c>
       <c r="Q141" t="n">
-        <v>-4.9</v>
+        <v>26.9</v>
       </c>
       <c r="R141" t="n">
-        <v>87.2</v>
+        <v>-32.8</v>
       </c>
     </row>
     <row r="142">
@@ -9498,12 +9496,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9520,10 +9518,10 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>15.5</v>
+        <v>83.3</v>
       </c>
       <c r="G143" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
@@ -9532,7 +9530,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -9541,27 +9539,27 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>15.8</v>
+        <v>1.6</v>
       </c>
       <c r="P143" t="n">
-        <v>-0.2</v>
+        <v>3.56</v>
       </c>
       <c r="Q143" t="n">
-        <v>152.7</v>
+        <v>18.8</v>
       </c>
       <c r="R143" t="n">
-        <v>65.40000000000001</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9578,10 +9576,10 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>83.3</v>
+        <v>15.5</v>
       </c>
       <c r="G144" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
@@ -9590,7 +9588,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -9599,27 +9597,27 @@
         </is>
       </c>
       <c r="O144" t="n">
-        <v>1.6</v>
+        <v>15.8</v>
       </c>
       <c r="P144" t="n">
-        <v>3.56</v>
+        <v>-0.2</v>
       </c>
       <c r="Q144" t="n">
-        <v>18.8</v>
+        <v>152.7</v>
       </c>
       <c r="R144" t="n">
-        <v>120.8</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>漢翔</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9636,10 +9634,10 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>61.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G145" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
@@ -9648,7 +9646,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -9657,27 +9655,25 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>4.2</v>
+        <v>11.6</v>
       </c>
       <c r="P145" t="n">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="Q145" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R145" t="n">
-        <v>-42.5</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>漢翔</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9694,10 +9690,10 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>65.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="G146" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
@@ -9706,7 +9702,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -9715,15 +9711,17 @@
         </is>
       </c>
       <c r="O146" t="n">
-        <v>11.6</v>
+        <v>4.2</v>
       </c>
       <c r="P146" t="n">
-        <v>1.62</v>
+        <v>3.15</v>
       </c>
       <c r="Q146" t="n">
-        <v>182</v>
-      </c>
-      <c r="R146" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="R146" t="n">
+        <v>-42.5</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9902,12 +9900,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9924,10 +9922,10 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>51.6</v>
+        <v>7.3</v>
       </c>
       <c r="G150" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -9945,27 +9943,27 @@
         </is>
       </c>
       <c r="O150" t="n">
-        <v>8.199999999999999</v>
+        <v>46.8</v>
       </c>
       <c r="P150" t="n">
-        <v>1.4</v>
+        <v>-2.61</v>
       </c>
       <c r="Q150" t="n">
-        <v>16</v>
+        <v>112.6</v>
       </c>
       <c r="R150" t="n">
-        <v>-4.3</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9982,10 +9980,10 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>7.3</v>
+        <v>94.8</v>
       </c>
       <c r="G151" t="n">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
@@ -9994,7 +9992,7 @@
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -10003,27 +10001,25 @@
         </is>
       </c>
       <c r="O151" t="n">
-        <v>46.8</v>
+        <v>4.8</v>
       </c>
       <c r="P151" t="n">
-        <v>-2.61</v>
+        <v>1.85</v>
       </c>
       <c r="Q151" t="n">
-        <v>112.6</v>
-      </c>
-      <c r="R151" t="n">
-        <v>96.59999999999999</v>
-      </c>
+        <v>605.5</v>
+      </c>
+      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10040,10 +10036,10 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>94.8</v>
+        <v>51.6</v>
       </c>
       <c r="G152" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -10052,7 +10048,7 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -10061,15 +10057,17 @@
         </is>
       </c>
       <c r="O152" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P152" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="Q152" t="n">
-        <v>605.5</v>
-      </c>
-      <c r="R152" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="R152" t="n">
+        <v>-4.3</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10248,12 +10246,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10270,10 +10268,10 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>16.9</v>
+        <v>103.6</v>
       </c>
       <c r="G156" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
@@ -10282,7 +10280,7 @@
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -10291,27 +10289,25 @@
         </is>
       </c>
       <c r="O156" t="n">
-        <v>13.1</v>
+        <v>3.9</v>
       </c>
       <c r="P156" t="n">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="Q156" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="R156" t="n">
-        <v>15.1</v>
-      </c>
+        <v>40.3</v>
+      </c>
+      <c r="R156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>晟銘電</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10328,10 +10324,10 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>589.2</v>
+        <v>20.2</v>
       </c>
       <c r="G157" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
@@ -10340,7 +10336,7 @@
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -10349,25 +10345,27 @@
         </is>
       </c>
       <c r="O157" t="n">
-        <v>0.5</v>
+        <v>17</v>
       </c>
       <c r="P157" t="n">
-        <v>9.07</v>
+        <v>0.68</v>
       </c>
       <c r="Q157" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="R157" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="R157" t="n">
+        <v>98.59999999999999</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10383,12 +10381,8 @@
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F158" t="n">
-        <v>19</v>
-      </c>
-      <c r="G158" t="n">
-        <v>5</v>
-      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
@@ -10396,36 +10390,34 @@
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 缺收盤/EPS</t>
         </is>
       </c>
       <c r="O158" t="n">
-        <v>15</v>
+        <v>-15.8</v>
       </c>
       <c r="P158" t="n">
-        <v>2.05</v>
+        <v>0.73</v>
       </c>
       <c r="Q158" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R158" t="n">
-        <v>-19.8</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="R158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10442,10 +10434,10 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>32.9</v>
+        <v>589.2</v>
       </c>
       <c r="G159" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -10463,27 +10455,25 @@
         </is>
       </c>
       <c r="O159" t="n">
-        <v>11.4</v>
+        <v>0.5</v>
       </c>
       <c r="P159" t="n">
-        <v>1.21</v>
+        <v>9.07</v>
       </c>
       <c r="Q159" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="R159" t="n">
-        <v>9</v>
-      </c>
+        <v>17.7</v>
+      </c>
+      <c r="R159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10499,8 +10489,12 @@
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="G160" t="n">
+        <v>100</v>
+      </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
@@ -10508,34 +10502,36 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>⏸ 缺收盤/EPS</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O160" t="n">
-        <v>-15.8</v>
+        <v>11.4</v>
       </c>
       <c r="P160" t="n">
-        <v>0.73</v>
+        <v>1.21</v>
       </c>
       <c r="Q160" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="R160" t="inlineStr"/>
+        <v>41.8</v>
+      </c>
+      <c r="R160" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10552,10 +10548,10 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>103.6</v>
+        <v>16.9</v>
       </c>
       <c r="G161" t="n">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -10564,7 +10560,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -10573,25 +10569,27 @@
         </is>
       </c>
       <c r="O161" t="n">
-        <v>3.9</v>
+        <v>13.1</v>
       </c>
       <c r="P161" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="Q161" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="R161" t="inlineStr"/>
+        <v>35.3</v>
+      </c>
+      <c r="R161" t="n">
+        <v>15.1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10608,7 +10606,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>20.2</v>
+        <v>19</v>
       </c>
       <c r="G162" t="n">
         <v>5</v>
@@ -10620,7 +10618,7 @@
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -10629,16 +10627,16 @@
         </is>
       </c>
       <c r="O162" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P162" t="n">
-        <v>0.68</v>
+        <v>2.05</v>
       </c>
       <c r="Q162" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="R162" t="n">
-        <v>98.59999999999999</v>
+        <v>-19.8</v>
       </c>
     </row>
     <row r="163">
@@ -10818,12 +10816,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>臺慶科</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10840,10 +10838,10 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>29.8</v>
+        <v>600</v>
       </c>
       <c r="G166" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -10861,27 +10859,25 @@
         </is>
       </c>
       <c r="O166" t="n">
-        <v>10.8</v>
+        <v>0.6</v>
       </c>
       <c r="P166" t="n">
-        <v>0.76</v>
+        <v>21.3</v>
       </c>
       <c r="Q166" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="R166" t="n">
-        <v>32.9</v>
-      </c>
+        <v>10.3</v>
+      </c>
+      <c r="R166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>臺慶科</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10898,7 +10894,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>115.6</v>
+        <v>29.8</v>
       </c>
       <c r="G167" t="n">
         <v>100</v>
@@ -10919,27 +10915,27 @@
         </is>
       </c>
       <c r="O167" t="n">
-        <v>12.4</v>
+        <v>10.8</v>
       </c>
       <c r="P167" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="Q167" t="n">
-        <v>21.3</v>
+        <v>37.8</v>
       </c>
       <c r="R167" t="n">
-        <v>12.1</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10956,10 +10952,10 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>600</v>
+        <v>115.6</v>
       </c>
       <c r="G168" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -10977,15 +10973,17 @@
         </is>
       </c>
       <c r="O168" t="n">
-        <v>0.6</v>
+        <v>12.4</v>
       </c>
       <c r="P168" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="Q168" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q168" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="R168" t="inlineStr"/>
+      <c r="R168" t="n">
+        <v>12.1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11048,12 +11046,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11070,10 +11068,10 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2019.2</v>
+        <v>46.4</v>
       </c>
       <c r="G170" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
@@ -11091,27 +11089,25 @@
         </is>
       </c>
       <c r="O170" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="P170" t="n">
-        <v>7.24</v>
+        <v>2.71</v>
       </c>
       <c r="Q170" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R170" t="n">
-        <v>-74.8</v>
-      </c>
+        <v>58.9</v>
+      </c>
+      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11128,10 +11124,10 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>46.4</v>
+        <v>2019.2</v>
       </c>
       <c r="G171" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
@@ -11149,25 +11145,27 @@
         </is>
       </c>
       <c r="O171" t="n">
-        <v>7.8</v>
+        <v>0.5</v>
       </c>
       <c r="P171" t="n">
-        <v>2.71</v>
+        <v>7.24</v>
       </c>
       <c r="Q171" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="R171" t="inlineStr"/>
+        <v>4.9</v>
+      </c>
+      <c r="R171" t="n">
+        <v>-74.8</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>晶彩科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11184,7 +11182,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>313.4</v>
+        <v>129.2</v>
       </c>
       <c r="G172" t="n">
         <v>99</v>
@@ -11205,25 +11203,27 @@
         </is>
       </c>
       <c r="O172" t="n">
-        <v>2.9</v>
+        <v>16</v>
       </c>
       <c r="P172" t="n">
-        <v>2.6</v>
+        <v>1.29</v>
       </c>
       <c r="Q172" t="n">
-        <v>2229</v>
-      </c>
-      <c r="R172" t="inlineStr"/>
+        <v>46.5</v>
+      </c>
+      <c r="R172" t="n">
+        <v>10.6</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>晶彩科</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>129.2</v>
+        <v>313.4</v>
       </c>
       <c r="G173" t="n">
         <v>99</v>
@@ -11261,17 +11261,15 @@
         </is>
       </c>
       <c r="O173" t="n">
-        <v>16</v>
+        <v>2.9</v>
       </c>
       <c r="P173" t="n">
-        <v>1.29</v>
+        <v>2.6</v>
       </c>
       <c r="Q173" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="R173" t="n">
-        <v>10.6</v>
-      </c>
+        <v>2229</v>
+      </c>
+      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11972,12 +11970,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>尚凡*</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11986,7 +11984,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -11994,10 +11992,10 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>19.8</v>
+        <v>25</v>
       </c>
       <c r="G186" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
@@ -12006,7 +12004,7 @@
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -12015,25 +12013,27 @@
         </is>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
-      </c>
-      <c r="P186" t="inlineStr"/>
+        <v>6.6</v>
+      </c>
+      <c r="P186" t="n">
+        <v>1.01</v>
+      </c>
       <c r="Q186" t="n">
-        <v>22.3</v>
+        <v>15</v>
       </c>
       <c r="R186" t="n">
-        <v>-0.2</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>尚凡*</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -12042,7 +12042,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -12050,10 +12050,10 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G187" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
@@ -12071,16 +12071,16 @@
         </is>
       </c>
       <c r="O187" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="P187" t="n">
-        <v>1.01</v>
+        <v>6.49</v>
       </c>
       <c r="Q187" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="R187" t="n">
-        <v>-72</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="188">
@@ -12144,12 +12144,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12166,10 +12166,10 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>27</v>
+        <v>2.6</v>
       </c>
       <c r="G189" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -12178,7 +12178,7 @@
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -12187,27 +12187,25 @@
         </is>
       </c>
       <c r="O189" t="n">
-        <v>17.5</v>
+        <v>37.9</v>
       </c>
       <c r="P189" t="n">
-        <v>6.49</v>
+        <v>0.01</v>
       </c>
       <c r="Q189" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="R189" t="n">
-        <v>2.6</v>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="R189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>豐達科</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12224,10 +12222,10 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2.6</v>
+        <v>23.3</v>
       </c>
       <c r="G190" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -12236,7 +12234,7 @@
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -12245,25 +12243,27 @@
         </is>
       </c>
       <c r="O190" t="n">
-        <v>37.9</v>
+        <v>9.4</v>
       </c>
       <c r="P190" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="Q190" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="R190" t="inlineStr"/>
+        <v>56.2</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>豐達科</t>
+          <t>緯軟</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12272,7 +12272,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>23.3</v>
+        <v>14.3</v>
       </c>
       <c r="G191" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -12292,7 +12292,7 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -12301,27 +12301,27 @@
         </is>
       </c>
       <c r="O191" t="n">
-        <v>9.4</v>
+        <v>15.9</v>
       </c>
       <c r="P191" t="n">
-        <v>0.04</v>
+        <v>0.53</v>
       </c>
       <c r="Q191" t="n">
-        <v>56.2</v>
+        <v>29.2</v>
       </c>
       <c r="R191" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>緯軟</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12338,10 +12338,10 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>14.3</v>
+        <v>12.7</v>
       </c>
       <c r="G192" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
@@ -12350,36 +12350,34 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 無成長率</t>
         </is>
       </c>
       <c r="O192" t="n">
-        <v>15.9</v>
+        <v>32</v>
       </c>
       <c r="P192" t="n">
-        <v>0.53</v>
+        <v>-0.39</v>
       </c>
       <c r="Q192" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="R192" t="n">
-        <v>-0.2</v>
-      </c>
+        <v>-72.7</v>
+      </c>
+      <c r="R192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>和亞智慧</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12388,7 +12386,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -12396,10 +12394,10 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>12.7</v>
+        <v>25.6</v>
       </c>
       <c r="G193" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
@@ -12408,34 +12406,36 @@
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>⏸ 無成長率</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O193" t="n">
-        <v>32</v>
+        <v>9.5</v>
       </c>
       <c r="P193" t="n">
-        <v>-0.39</v>
+        <v>2.12</v>
       </c>
       <c r="Q193" t="n">
-        <v>-72.7</v>
-      </c>
-      <c r="R193" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="R193" t="n">
+        <v>-10.3</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>晶瑞光</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12451,12 +12451,8 @@
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F194" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G194" t="n">
-        <v>69</v>
-      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
@@ -12464,36 +12460,34 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 缺收盤/EPS</t>
         </is>
       </c>
       <c r="O194" t="n">
-        <v>9.5</v>
+        <v>-66.09999999999999</v>
       </c>
       <c r="P194" t="n">
-        <v>2.12</v>
+        <v>0.57</v>
       </c>
       <c r="Q194" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="R194" t="n">
-        <v>-10.3</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="R194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>晶瑞光</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12502,15 +12496,19 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
+      <c r="F195" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="G195" t="n">
+        <v>90</v>
+      </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
@@ -12518,34 +12516,36 @@
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>⏸ 缺收盤/EPS</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O195" t="n">
-        <v>-66.09999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="P195" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="Q195" t="n">
-        <v>58</v>
-      </c>
-      <c r="R195" t="inlineStr"/>
+        <v>10.6</v>
+      </c>
+      <c r="R195" t="n">
+        <v>-6.5</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>新鉅科</t>
+          <t>中工</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12562,10 +12562,10 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>16</v>
+        <v>27.2</v>
       </c>
       <c r="G196" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
@@ -12583,25 +12583,27 @@
         </is>
       </c>
       <c r="O196" t="n">
-        <v>14.4</v>
+        <v>3.3</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.18</v>
+        <v>-0.92</v>
       </c>
       <c r="Q196" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R196" t="inlineStr"/>
+        <v>57.1</v>
+      </c>
+      <c r="R196" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>新鉅科</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12618,10 +12620,10 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>30.2</v>
+        <v>16</v>
       </c>
       <c r="G197" t="n">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
@@ -12630,7 +12632,7 @@
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -12639,27 +12641,25 @@
         </is>
       </c>
       <c r="O197" t="n">
-        <v>6.2</v>
+        <v>14.4</v>
       </c>
       <c r="P197" t="n">
-        <v>0.7</v>
+        <v>-0.18</v>
       </c>
       <c r="Q197" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="R197" t="n">
-        <v>-6.5</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="R197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12668,7 +12668,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>27.2</v>
+        <v>87.5</v>
       </c>
       <c r="G198" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -12697,27 +12697,27 @@
         </is>
       </c>
       <c r="O198" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="P198" t="n">
-        <v>-0.92</v>
+        <v>7.96</v>
       </c>
       <c r="Q198" t="n">
-        <v>57.1</v>
+        <v>73.8</v>
       </c>
       <c r="R198" t="n">
-        <v>-1.2</v>
+        <v>-30.3</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12726,7 +12726,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -12734,10 +12734,10 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>87.5</v>
+        <v>19.8</v>
       </c>
       <c r="G199" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
@@ -12746,7 +12746,7 @@
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -12755,27 +12755,27 @@
         </is>
       </c>
       <c r="O199" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="P199" t="n">
-        <v>7.96</v>
+        <v>2.28</v>
       </c>
       <c r="Q199" t="n">
-        <v>73.8</v>
+        <v>12</v>
       </c>
       <c r="R199" t="n">
-        <v>-30.3</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12792,10 +12792,10 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>19.8</v>
+        <v>41.4</v>
       </c>
       <c r="G200" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
@@ -12804,7 +12804,7 @@
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -12813,16 +12813,16 @@
         </is>
       </c>
       <c r="O200" t="n">
-        <v>6.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P200" t="n">
-        <v>2.28</v>
+        <v>-0.65</v>
       </c>
       <c r="Q200" t="n">
-        <v>12</v>
+        <v>-11.2</v>
       </c>
       <c r="R200" t="n">
-        <v>-4.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="201">
@@ -12880,12 +12880,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>立凱-KY</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>41.4</v>
+        <v>121.1</v>
       </c>
       <c r="G202" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
@@ -12923,17 +12923,15 @@
         </is>
       </c>
       <c r="O202" t="n">
-        <v>9.300000000000001</v>
+        <v>-11.5</v>
       </c>
       <c r="P202" t="n">
-        <v>-0.65</v>
+        <v>7.37</v>
       </c>
       <c r="Q202" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="R202" t="n">
-        <v>2.8</v>
-      </c>
+        <v>-97.09999999999999</v>
+      </c>
+      <c r="R202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12996,12 +12994,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>立凱-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -13018,10 +13016,10 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>121.1</v>
+        <v>192.6</v>
       </c>
       <c r="G204" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
@@ -13039,25 +13037,27 @@
         </is>
       </c>
       <c r="O204" t="n">
-        <v>-11.5</v>
+        <v>6.5</v>
       </c>
       <c r="P204" t="n">
-        <v>7.37</v>
+        <v>1.46</v>
       </c>
       <c r="Q204" t="n">
-        <v>-97.09999999999999</v>
-      </c>
-      <c r="R204" t="inlineStr"/>
+        <v>35.8</v>
+      </c>
+      <c r="R204" t="n">
+        <v>-42.1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -13074,10 +13074,10 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>192.6</v>
+        <v>132.8</v>
       </c>
       <c r="G205" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -13095,27 +13095,25 @@
         </is>
       </c>
       <c r="O205" t="n">
-        <v>6.5</v>
+        <v>-0.3</v>
       </c>
       <c r="P205" t="n">
-        <v>1.46</v>
+        <v>-41.26</v>
       </c>
       <c r="Q205" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="R205" t="n">
-        <v>-42.1</v>
-      </c>
+        <v>16.1</v>
+      </c>
+      <c r="R205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13124,7 +13122,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -13132,10 +13130,10 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>132.8</v>
+        <v>476.9</v>
       </c>
       <c r="G206" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
@@ -13144,7 +13142,7 @@
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -13153,25 +13151,27 @@
         </is>
       </c>
       <c r="O206" t="n">
-        <v>-0.3</v>
+        <v>1.3</v>
       </c>
       <c r="P206" t="n">
-        <v>-41.26</v>
+        <v>6.65</v>
       </c>
       <c r="Q206" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="R206" t="inlineStr"/>
+        <v>24.4</v>
+      </c>
+      <c r="R206" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>三福化</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13188,10 +13188,10 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>476.9</v>
+        <v>38.4</v>
       </c>
       <c r="G207" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
@@ -13200,7 +13200,7 @@
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -13209,27 +13209,27 @@
         </is>
       </c>
       <c r="O207" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="P207" t="n">
-        <v>6.65</v>
+        <v>2.91</v>
       </c>
       <c r="Q207" t="n">
-        <v>24.4</v>
+        <v>-5.8</v>
       </c>
       <c r="R207" t="n">
-        <v>-58</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>三福化</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -13246,10 +13246,10 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>38.4</v>
+        <v>278.3</v>
       </c>
       <c r="G208" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
@@ -13258,26 +13258,22 @@
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 無成長率</t>
         </is>
       </c>
       <c r="O208" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="P208" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="R208" t="n">
-        <v>-8.4</v>
-      </c>
+        <v>-0.32</v>
+      </c>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13340,12 +13336,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13354,7 +13350,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -13362,10 +13358,10 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>278.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G210" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
@@ -13379,27 +13375,31 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>⏸ 無成長率</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O210" t="n">
-        <v>25</v>
+        <v>3.3</v>
       </c>
       <c r="P210" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="inlineStr"/>
+        <v>3.98</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="R210" t="n">
+        <v>-48.1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13416,10 +13416,10 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>43.6</v>
+        <v>37.2</v>
       </c>
       <c r="G211" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
@@ -13428,36 +13428,36 @@
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-16%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O211" t="n">
-        <v>10.9</v>
+        <v>2.9</v>
       </c>
       <c r="P211" t="n">
-        <v>2.01</v>
+        <v>0.26</v>
       </c>
       <c r="Q211" t="n">
-        <v>30.2</v>
+        <v>23</v>
       </c>
       <c r="R211" t="n">
-        <v>-16.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>訊聯</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>68.8</v>
+        <v>43.6</v>
       </c>
       <c r="G212" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
@@ -13486,36 +13486,36 @@
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-16%)</t>
         </is>
       </c>
       <c r="O212" t="n">
-        <v>-0.2</v>
+        <v>10.9</v>
       </c>
       <c r="P212" t="n">
-        <v>-52.8</v>
+        <v>2.01</v>
       </c>
       <c r="Q212" t="n">
-        <v>15</v>
+        <v>30.2</v>
       </c>
       <c r="R212" t="n">
-        <v>-21.8</v>
+        <v>-16.5</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13532,10 +13532,10 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>96.59999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="G213" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
@@ -13544,7 +13544,7 @@
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -13553,16 +13553,16 @@
         </is>
       </c>
       <c r="O213" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="P213" t="n">
-        <v>3.98</v>
+        <v>0.12</v>
       </c>
       <c r="Q213" t="n">
-        <v>17.7</v>
+        <v>199.6</v>
       </c>
       <c r="R213" t="n">
-        <v>-48.1</v>
+        <v>-62.2</v>
       </c>
     </row>
     <row r="214">
@@ -13626,12 +13626,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>訊聯</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13648,10 +13648,10 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>37.2</v>
+        <v>68.8</v>
       </c>
       <c r="G215" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr"/>
@@ -13660,7 +13660,7 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -13669,27 +13669,27 @@
         </is>
       </c>
       <c r="O215" t="n">
-        <v>2.9</v>
+        <v>-0.2</v>
       </c>
       <c r="P215" t="n">
-        <v>0.26</v>
+        <v>-52.8</v>
       </c>
       <c r="Q215" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="R215" t="n">
-        <v>24.6</v>
+        <v>-21.8</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -13706,10 +13706,10 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>20.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G216" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr"/>
@@ -13718,26 +13718,22 @@
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 無成長率</t>
         </is>
       </c>
       <c r="O216" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P216" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>199.6</v>
-      </c>
-      <c r="R216" t="n">
-        <v>-62.2</v>
-      </c>
+        <v>1.78</v>
+      </c>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13800,12 +13796,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13814,7 +13810,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -13822,10 +13818,10 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>9.699999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="G218" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr"/>
@@ -13834,32 +13830,36 @@
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>⏸ 無成長率</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O218" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="P218" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q218" t="inlineStr"/>
-      <c r="R218" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="R218" t="n">
+        <v>-24.9</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>世豐</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13868,7 +13868,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>40.2</v>
+        <v>27.6</v>
       </c>
       <c r="G219" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
@@ -13888,7 +13888,7 @@
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -13897,16 +13897,16 @@
         </is>
       </c>
       <c r="O219" t="n">
-        <v>9.9</v>
+        <v>4.4</v>
       </c>
       <c r="P219" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q219" t="n">
-        <v>26.9</v>
+        <v>18.6</v>
       </c>
       <c r="R219" t="n">
-        <v>-24.9</v>
+        <v>-52.9</v>
       </c>
     </row>
     <row r="220">
@@ -14028,12 +14028,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>世豐</t>
+          <t>三圓</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14042,7 +14042,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -14050,10 +14050,10 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>27.6</v>
+        <v>11.6</v>
       </c>
       <c r="G222" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
@@ -14062,7 +14062,7 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -14071,27 +14071,25 @@
         </is>
       </c>
       <c r="O222" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P222" t="n">
-        <v>1.53</v>
+        <v>0.32</v>
       </c>
       <c r="Q222" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="R222" t="n">
-        <v>-52.9</v>
-      </c>
+        <v>-21.5</v>
+      </c>
+      <c r="R222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14108,10 +14106,10 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>18.1</v>
+        <v>25.8</v>
       </c>
       <c r="G223" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
@@ -14120,7 +14118,7 @@
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -14129,27 +14127,27 @@
         </is>
       </c>
       <c r="O223" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="P223" t="n">
-        <v>0.76</v>
+        <v>-2.99</v>
       </c>
       <c r="Q223" t="n">
-        <v>-3.3</v>
+        <v>36.5</v>
       </c>
       <c r="R223" t="n">
-        <v>1.2</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14166,10 +14164,10 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>44.3</v>
+        <v>19.9</v>
       </c>
       <c r="G224" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
@@ -14187,27 +14185,27 @@
         </is>
       </c>
       <c r="O224" t="n">
-        <v>7.9</v>
+        <v>15.4</v>
       </c>
       <c r="P224" t="n">
-        <v>3.85</v>
+        <v>1.55</v>
       </c>
       <c r="Q224" t="n">
-        <v>19.5</v>
+        <v>39.8</v>
       </c>
       <c r="R224" t="n">
-        <v>-2.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>三圓</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14224,10 +14222,10 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>11.6</v>
+        <v>18.1</v>
       </c>
       <c r="G225" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
@@ -14236,7 +14234,7 @@
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -14245,25 +14243,27 @@
         </is>
       </c>
       <c r="O225" t="n">
-        <v>3.5</v>
+        <v>17.5</v>
       </c>
       <c r="P225" t="n">
-        <v>0.32</v>
+        <v>0.76</v>
       </c>
       <c r="Q225" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="R225" t="inlineStr"/>
+        <v>-3.3</v>
+      </c>
+      <c r="R225" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14280,10 +14280,10 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>25.8</v>
+        <v>18</v>
       </c>
       <c r="G226" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
@@ -14292,7 +14292,7 @@
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -14301,27 +14301,25 @@
         </is>
       </c>
       <c r="O226" t="n">
-        <v>6.6</v>
+        <v>-1.3</v>
       </c>
       <c r="P226" t="n">
-        <v>-2.99</v>
+        <v>-11.39</v>
       </c>
       <c r="Q226" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="R226" t="n">
-        <v>-12.3</v>
-      </c>
+        <v>175.8</v>
+      </c>
+      <c r="R226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14338,10 +14336,10 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>19.9</v>
+        <v>44.3</v>
       </c>
       <c r="G227" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
@@ -14359,27 +14357,27 @@
         </is>
       </c>
       <c r="O227" t="n">
-        <v>15.4</v>
+        <v>7.9</v>
       </c>
       <c r="P227" t="n">
-        <v>1.55</v>
+        <v>3.85</v>
       </c>
       <c r="Q227" t="n">
-        <v>39.8</v>
+        <v>19.5</v>
       </c>
       <c r="R227" t="n">
-        <v>-2.8</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>全坤建</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14388,7 +14386,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -14396,7 +14394,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="G228" t="n">
         <v>91</v>
@@ -14408,7 +14406,7 @@
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -14417,13 +14415,13 @@
         </is>
       </c>
       <c r="O228" t="n">
-        <v>-1.3</v>
+        <v>-4.6</v>
       </c>
       <c r="P228" t="n">
-        <v>-11.39</v>
+        <v>10.68</v>
       </c>
       <c r="Q228" t="n">
-        <v>175.8</v>
+        <v>-0.7</v>
       </c>
       <c r="R228" t="inlineStr"/>
     </row>
@@ -14546,12 +14544,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>全坤建</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14560,7 +14558,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -14568,10 +14566,10 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>220</v>
+        <v>18.8</v>
       </c>
       <c r="G231" t="n">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
@@ -14580,7 +14578,7 @@
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -14589,25 +14587,27 @@
         </is>
       </c>
       <c r="O231" t="n">
-        <v>-4.6</v>
+        <v>6.1</v>
       </c>
       <c r="P231" t="n">
-        <v>10.68</v>
+        <v>-2.09</v>
       </c>
       <c r="Q231" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="R231" t="inlineStr"/>
+        <v>-14.8</v>
+      </c>
+      <c r="R231" t="n">
+        <v>13.7</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14624,10 +14624,10 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>18.8</v>
+        <v>127.5</v>
       </c>
       <c r="G232" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
@@ -14636,7 +14636,7 @@
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -14645,27 +14645,27 @@
         </is>
       </c>
       <c r="O232" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P232" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q232" t="n">
         <v>6.1</v>
       </c>
-      <c r="P232" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="Q232" t="n">
-        <v>-14.8</v>
-      </c>
       <c r="R232" t="n">
-        <v>13.7</v>
+        <v>-48.3</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -14682,10 +14682,10 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>127.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G233" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
@@ -14694,7 +14694,7 @@
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -14703,27 +14703,27 @@
         </is>
       </c>
       <c r="O233" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="P233" t="n">
-        <v>3.75</v>
+        <v>1.05</v>
       </c>
       <c r="Q233" t="n">
-        <v>6.1</v>
+        <v>19.1</v>
       </c>
       <c r="R233" t="n">
-        <v>-48.3</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -14740,10 +14740,10 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>75.40000000000001</v>
+        <v>22.3</v>
       </c>
       <c r="G234" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -14761,27 +14761,27 @@
         </is>
       </c>
       <c r="O234" t="n">
-        <v>5.4</v>
+        <v>20.6</v>
       </c>
       <c r="P234" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Q234" t="n">
-        <v>19.1</v>
+        <v>9.4</v>
       </c>
       <c r="R234" t="n">
-        <v>-17</v>
+        <v>-16.3</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -14798,10 +14798,10 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>22.3</v>
+        <v>5637.5</v>
       </c>
       <c r="G235" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
@@ -14810,7 +14810,7 @@
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -14819,16 +14819,16 @@
         </is>
       </c>
       <c r="O235" t="n">
-        <v>20.6</v>
+        <v>-1.6</v>
       </c>
       <c r="P235" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="Q235" t="n">
-        <v>9.4</v>
+        <v>-24.8</v>
       </c>
       <c r="R235" t="n">
-        <v>-16.3</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="236">
@@ -14892,12 +14892,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14906,7 +14906,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -14914,10 +14914,10 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>5637.5</v>
+        <v>251.2</v>
       </c>
       <c r="G237" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
@@ -14935,17 +14935,15 @@
         </is>
       </c>
       <c r="O237" t="n">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="P237" t="n">
-        <v>0.97</v>
+        <v>-3.66</v>
       </c>
       <c r="Q237" t="n">
-        <v>-24.8</v>
-      </c>
-      <c r="R237" t="n">
-        <v>15.5</v>
-      </c>
+        <v>140.2</v>
+      </c>
+      <c r="R237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15058,12 +15056,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>大同</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15080,10 +15078,10 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>251.2</v>
+        <v>7.7</v>
       </c>
       <c r="G240" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
@@ -15092,7 +15090,7 @@
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -15101,25 +15099,25 @@
         </is>
       </c>
       <c r="O240" t="n">
-        <v>-2.4</v>
+        <v>-21.2</v>
       </c>
       <c r="P240" t="n">
-        <v>-3.66</v>
+        <v>-0.09</v>
       </c>
       <c r="Q240" t="n">
-        <v>140.2</v>
+        <v>-14.3</v>
       </c>
       <c r="R240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>大同</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15128,19 +15126,15 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F241" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G241" t="n">
-        <v>25</v>
-      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
@@ -15148,34 +15142,30 @@
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O241" t="n">
-        <v>-21.2</v>
-      </c>
+          <t>⏸ 缺收盤/EPS</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr"/>
       <c r="P241" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>-14.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15192,10 +15182,10 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>4.98045135262149e+17</v>
+        <v>275</v>
       </c>
       <c r="G242" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
@@ -15204,7 +15194,7 @@
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -15213,25 +15203,27 @@
         </is>
       </c>
       <c r="O242" t="n">
-        <v>-9.1</v>
+        <v>-0.1</v>
       </c>
       <c r="P242" t="n">
-        <v>-0.63</v>
+        <v>-15.71</v>
       </c>
       <c r="Q242" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="R242" t="inlineStr"/>
+        <v>15.3</v>
+      </c>
+      <c r="R242" t="n">
+        <v>-56.7</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15247,8 +15239,12 @@
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
+      <c r="F243" t="n">
+        <v>4.98045135262149e+17</v>
+      </c>
+      <c r="G243" t="n">
+        <v>73</v>
+      </c>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
@@ -15256,30 +15252,34 @@
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>⏸ 缺收盤/EPS</t>
-        </is>
-      </c>
-      <c r="O243" t="inlineStr"/>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O243" t="n">
+        <v>-9.1</v>
+      </c>
       <c r="P243" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q243" t="inlineStr"/>
+        <v>-0.63</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>56.3</v>
+      </c>
       <c r="R243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -15296,10 +15296,10 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>275</v>
+        <v>93.3</v>
       </c>
       <c r="G244" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
@@ -15308,36 +15308,32 @@
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 無成長率</t>
         </is>
       </c>
       <c r="O244" t="n">
-        <v>-0.1</v>
+        <v>7.3</v>
       </c>
       <c r="P244" t="n">
-        <v>-15.71</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="R244" t="n">
-        <v>-56.7</v>
-      </c>
+        <v>0.51</v>
+      </c>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>潤泰全</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15354,10 +15350,10 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>93.3</v>
+        <v>6</v>
       </c>
       <c r="G245" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
@@ -15366,32 +15362,36 @@
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>⏸ 無成長率</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O245" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="P245" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="R245" t="n">
+        <v>13.7</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>潤泰全</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>6</v>
+        <v>36.1</v>
       </c>
       <c r="G246" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
@@ -15420,7 +15420,7 @@
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -15429,27 +15429,27 @@
         </is>
       </c>
       <c r="O246" t="n">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="Q246" t="n">
-        <v>-21.8</v>
+        <v>58.4</v>
       </c>
       <c r="R246" t="n">
-        <v>13.7</v>
+        <v>-34.5</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -15466,10 +15466,10 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>36.1</v>
+        <v>194.5</v>
       </c>
       <c r="G247" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
@@ -15478,7 +15478,7 @@
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -15487,27 +15487,27 @@
         </is>
       </c>
       <c r="O247" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="P247" t="n">
-        <v>1.42</v>
+        <v>-1.6</v>
       </c>
       <c r="Q247" t="n">
-        <v>58.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="R247" t="n">
-        <v>-34.5</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>奈米醫材</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15524,10 +15524,10 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>194.5</v>
+        <v>85.8</v>
       </c>
       <c r="G248" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
@@ -15536,7 +15536,7 @@
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -15545,27 +15545,27 @@
         </is>
       </c>
       <c r="O248" t="n">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
       <c r="P248" t="n">
-        <v>-1.6</v>
+        <v>-1.67</v>
       </c>
       <c r="Q248" t="n">
-        <v>69.09999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="R248" t="n">
-        <v>-13.4</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>光環</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -15582,10 +15582,10 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>85.8</v>
+        <v>308.3</v>
       </c>
       <c r="G249" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
@@ -15603,27 +15603,25 @@
         </is>
       </c>
       <c r="O249" t="n">
-        <v>-0.5</v>
+        <v>-27.9</v>
       </c>
       <c r="P249" t="n">
-        <v>-1.67</v>
+        <v>0.12</v>
       </c>
       <c r="Q249" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="R249" t="n">
-        <v>-36</v>
-      </c>
+        <v>13.3</v>
+      </c>
+      <c r="R249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15632,7 +15630,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -15640,10 +15638,10 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>308.3</v>
+        <v>68.7</v>
       </c>
       <c r="G250" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
@@ -15652,7 +15650,7 @@
       <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -15661,15 +15659,17 @@
         </is>
       </c>
       <c r="O250" t="n">
-        <v>-27.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P250" t="n">
-        <v>0.12</v>
+        <v>1.6</v>
       </c>
       <c r="Q250" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="R250" t="inlineStr"/>
+        <v>-3.3</v>
+      </c>
+      <c r="R250" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15730,12 +15730,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>晶呈科技</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15744,7 +15744,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -15752,10 +15752,10 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>68.7</v>
+        <v>1184.6</v>
       </c>
       <c r="G252" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
@@ -15773,27 +15773,27 @@
         </is>
       </c>
       <c r="O252" t="n">
-        <v>8.300000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="P252" t="n">
-        <v>1.6</v>
+        <v>-12.96</v>
       </c>
       <c r="Q252" t="n">
-        <v>-3.3</v>
+        <v>64.2</v>
       </c>
       <c r="R252" t="n">
-        <v>-42</v>
+        <v>-62.8</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>晶呈科技</t>
+          <t>川寶</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -15810,10 +15810,10 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1184.6</v>
+        <v>253.5</v>
       </c>
       <c r="G253" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
@@ -15831,27 +15831,25 @@
         </is>
       </c>
       <c r="O253" t="n">
-        <v>-1.3</v>
+        <v>-4.7</v>
       </c>
       <c r="P253" t="n">
-        <v>-12.96</v>
+        <v>0.64</v>
       </c>
       <c r="Q253" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="R253" t="n">
-        <v>-62.8</v>
-      </c>
+        <v>173.8</v>
+      </c>
+      <c r="R253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>川寶</t>
+          <t>正達</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15860,19 +15858,15 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F254" t="n">
-        <v>253.5</v>
-      </c>
-      <c r="G254" t="n">
-        <v>98</v>
-      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
@@ -15889,25 +15883,25 @@
         </is>
       </c>
       <c r="O254" t="n">
-        <v>-4.7</v>
+        <v>-21.9</v>
       </c>
       <c r="P254" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="Q254" t="n">
-        <v>173.8</v>
+        <v>-6.7</v>
       </c>
       <c r="R254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>正達</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15916,15 +15910,19 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
+      <c r="F255" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G255" t="n">
+        <v>93</v>
+      </c>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
@@ -15932,24 +15930,26 @@
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-4%)</t>
         </is>
       </c>
       <c r="O255" t="n">
-        <v>-21.9</v>
+        <v>15.5</v>
       </c>
       <c r="P255" t="n">
-        <v>0.72</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="Q255" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="R255" t="inlineStr"/>
+        <v>-24.3</v>
+      </c>
+      <c r="R255" t="n">
+        <v>-4.3</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -16012,12 +16012,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16026,7 +16026,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>15.4</v>
+        <v>65.8</v>
       </c>
       <c r="G257" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
@@ -16051,31 +16051,29 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-4%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="O257" t="n">
-        <v>15.5</v>
+        <v>-7.2</v>
       </c>
       <c r="P257" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="Q257" t="n">
-        <v>-24.3</v>
-      </c>
-      <c r="R257" t="n">
-        <v>-4.3</v>
-      </c>
+        <v>-13.9</v>
+      </c>
+      <c r="R257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16084,7 +16082,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -16092,10 +16090,10 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>65.8</v>
+        <v>83.5</v>
       </c>
       <c r="G258" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
@@ -16109,29 +16107,29 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-50%)</t>
         </is>
       </c>
       <c r="O258" t="n">
-        <v>-7.2</v>
+        <v>6.1</v>
       </c>
       <c r="P258" t="n">
-        <v>-0.67</v>
+        <v>-0.57</v>
       </c>
       <c r="Q258" t="n">
-        <v>-13.9</v>
+        <v>19.9</v>
       </c>
       <c r="R258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16147,8 +16145,12 @@
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="F259" t="n">
+        <v>2725</v>
+      </c>
+      <c r="G259" t="n">
+        <v>81</v>
+      </c>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
@@ -16156,17 +16158,23 @@
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>⏸ 缺收盤/EPS</t>
-        </is>
-      </c>
-      <c r="O259" t="inlineStr"/>
-      <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="inlineStr"/>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O259" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>-66.8</v>
+      </c>
       <c r="R259" t="inlineStr"/>
     </row>
     <row r="260">
@@ -16218,12 +16226,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16239,12 +16247,8 @@
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F261" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="G261" t="n">
-        <v>93</v>
-      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
@@ -16252,34 +16256,28 @@
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-50%)</t>
-        </is>
-      </c>
-      <c r="O261" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="P261" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="Q261" t="n">
-        <v>19.9</v>
-      </c>
+          <t>⏸ 缺收盤/EPS</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16295,12 +16293,8 @@
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F262" t="n">
-        <v>2725</v>
-      </c>
-      <c r="G262" t="n">
-        <v>81</v>
-      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
@@ -16308,51 +16302,47 @@
       <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O262" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="P262" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="Q262" t="n">
-        <v>-66.8</v>
-      </c>
+          <t>⏸ 缺收盤/EPS</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>群益證</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>0</v>
-      </c>
+          <t>金融🏦</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
+      <c r="F263" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G263" t="n">
+        <v>61</v>
+      </c>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
@@ -16360,28 +16350,36 @@
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>⏸ 缺收盤/EPS</t>
-        </is>
-      </c>
-      <c r="O263" t="inlineStr"/>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
-      <c r="R263" t="inlineStr"/>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O263" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="P263" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="R263" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>群益證</t>
+          <t>中再保</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16396,10 +16394,10 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="G264" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
@@ -16417,27 +16415,27 @@
         </is>
       </c>
       <c r="O264" t="n">
-        <v>15.9</v>
+        <v>17.6</v>
       </c>
       <c r="P264" t="n">
-        <v>-1.41</v>
+        <v>2.22</v>
       </c>
       <c r="Q264" t="n">
-        <v>155.5</v>
+        <v>170.2</v>
       </c>
       <c r="R264" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>中再保</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16452,10 +16450,10 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>10.7</v>
+        <v>17.3</v>
       </c>
       <c r="G265" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
@@ -16473,27 +16471,27 @@
         </is>
       </c>
       <c r="O265" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="P265" t="n">
-        <v>2.22</v>
+        <v>-1.14</v>
       </c>
       <c r="Q265" t="n">
-        <v>170.2</v>
+        <v>428.4</v>
       </c>
       <c r="R265" t="n">
-        <v>18.4</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16508,7 +16506,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="G266" t="n">
         <v>82</v>
@@ -16529,27 +16527,25 @@
         </is>
       </c>
       <c r="O266" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="P266" t="n">
-        <v>-1.14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P266" t="inlineStr"/>
       <c r="Q266" t="n">
-        <v>428.4</v>
+        <v>117.9</v>
       </c>
       <c r="R266" t="n">
-        <v>23.1</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16564,10 +16560,10 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="G267" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
@@ -16589,21 +16585,21 @@
       </c>
       <c r="P267" t="inlineStr"/>
       <c r="Q267" t="n">
-        <v>117.9</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R267" t="n">
-        <v>37.5</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16618,10 +16614,10 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>17.3</v>
+        <v>25.1</v>
       </c>
       <c r="G268" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
@@ -16643,21 +16639,21 @@
       </c>
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="n">
-        <v>76.09999999999999</v>
+        <v>227.3</v>
       </c>
       <c r="R268" t="n">
-        <v>20.3</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16672,10 +16668,10 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>25.1</v>
+        <v>16</v>
       </c>
       <c r="G269" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
@@ -16697,21 +16693,21 @@
       </c>
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="n">
-        <v>227.3</v>
+        <v>28.8</v>
       </c>
       <c r="R269" t="n">
-        <v>14.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16726,10 +16722,10 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>16</v>
+        <v>19.8</v>
       </c>
       <c r="G270" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
@@ -16751,10 +16747,10 @@
       </c>
       <c r="P270" t="inlineStr"/>
       <c r="Q270" t="n">
-        <v>28.8</v>
+        <v>22.3</v>
       </c>
       <c r="R270" t="n">
-        <v>47.6</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="271">
@@ -21092,12 +21088,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -21114,10 +21110,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>66.5</v>
+        <v>24</v>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -21135,27 +21131,27 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>34.3</v>
+        <v>29.3</v>
       </c>
       <c r="P61" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Q61" t="n">
-        <v>172.1</v>
+        <v>25</v>
       </c>
       <c r="R61" t="n">
-        <v>90.7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -21172,10 +21168,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>77.09999999999999</v>
+        <v>163.5</v>
       </c>
       <c r="G62" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -21193,27 +21189,27 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>29.3</v>
+        <v>74.7</v>
       </c>
       <c r="P62" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Q62" t="n">
-        <v>116</v>
+        <v>68.7</v>
       </c>
       <c r="R62" t="n">
-        <v>204.6</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -21230,10 +21226,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>163.5</v>
+        <v>66.5</v>
       </c>
       <c r="G63" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -21251,27 +21247,27 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>74.7</v>
+        <v>34.3</v>
       </c>
       <c r="P63" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>68.7</v>
+        <v>172.1</v>
       </c>
       <c r="R63" t="n">
-        <v>97.40000000000001</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -21288,10 +21284,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>24</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -21312,13 +21308,13 @@
         <v>29.3</v>
       </c>
       <c r="P64" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Q64" t="n">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="R64" t="n">
-        <v>49</v>
+        <v>204.6</v>
       </c>
     </row>
     <row r="65">
@@ -21730,12 +21726,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -21752,10 +21748,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>12.2</v>
+        <v>27.9</v>
       </c>
       <c r="G72" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -21764,7 +21760,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -21773,27 +21769,27 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>20</v>
+        <v>28.8</v>
       </c>
       <c r="P72" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Q72" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="R72" t="n">
-        <v>16.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -21810,10 +21806,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>27.9</v>
+        <v>12.2</v>
       </c>
       <c r="G73" t="n">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -21822,7 +21818,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -21831,27 +21827,27 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>28.8</v>
+        <v>20</v>
       </c>
       <c r="P73" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Q73" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="R73" t="n">
-        <v>36.5</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -21868,10 +21864,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>72.7</v>
+        <v>45.8</v>
       </c>
       <c r="G74" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -21889,27 +21885,27 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>48.1</v>
+        <v>14.4</v>
       </c>
       <c r="P74" t="n">
-        <v>0.31</v>
+        <v>1.62</v>
       </c>
       <c r="Q74" t="n">
-        <v>133.1</v>
+        <v>13</v>
       </c>
       <c r="R74" t="n">
-        <v>71.09999999999999</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -21926,10 +21922,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>45.8</v>
+        <v>72.7</v>
       </c>
       <c r="G75" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -21947,16 +21943,16 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>14.4</v>
+        <v>48.1</v>
       </c>
       <c r="P75" t="n">
-        <v>1.62</v>
+        <v>0.31</v>
       </c>
       <c r="Q75" t="n">
-        <v>13</v>
+        <v>133.1</v>
       </c>
       <c r="R75" t="n">
-        <v>25.5</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -22426,12 +22422,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>王品</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -22448,10 +22444,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>310.9</v>
+        <v>14.8</v>
       </c>
       <c r="G84" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
@@ -22460,7 +22456,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -22469,25 +22465,27 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>16.6</v>
+        <v>33.6</v>
       </c>
       <c r="P84" t="n">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="Q84" t="n">
-        <v>118.8</v>
-      </c>
-      <c r="R84" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="R84" t="n">
+        <v>-4.8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>王品</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -22504,10 +22502,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>14.8</v>
+        <v>310.9</v>
       </c>
       <c r="G85" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -22516,7 +22514,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -22525,27 +22523,25 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>33.6</v>
+        <v>16.6</v>
       </c>
       <c r="P85" t="n">
-        <v>2.56</v>
+        <v>1.13</v>
       </c>
       <c r="Q85" t="n">
-        <v>15</v>
-      </c>
-      <c r="R85" t="n">
-        <v>-4.8</v>
-      </c>
+        <v>118.8</v>
+      </c>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -22562,10 +22558,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>25.5</v>
+        <v>10.5</v>
       </c>
       <c r="G86" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -22574,7 +22570,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -22583,16 +22579,16 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>17.9</v>
+        <v>41.3</v>
       </c>
       <c r="P86" t="n">
-        <v>1.71</v>
+        <v>-1.31</v>
       </c>
       <c r="Q86" t="n">
-        <v>19</v>
+        <v>224.4</v>
       </c>
       <c r="R86" t="n">
-        <v>15.6</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="87">
@@ -22656,12 +22652,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -22678,10 +22674,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
       <c r="G88" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -22690,7 +22686,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -22699,27 +22695,27 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>41.3</v>
+        <v>17.9</v>
       </c>
       <c r="P88" t="n">
-        <v>-1.31</v>
+        <v>1.71</v>
       </c>
       <c r="Q88" t="n">
-        <v>224.4</v>
+        <v>19</v>
       </c>
       <c r="R88" t="n">
-        <v>21.9</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -22736,7 +22732,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>62.1</v>
+        <v>36.3</v>
       </c>
       <c r="G89" t="n">
         <v>100</v>
@@ -22757,27 +22753,27 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>12.8</v>
+        <v>14.6</v>
       </c>
       <c r="P89" t="n">
-        <v>3.26</v>
+        <v>1.81</v>
       </c>
       <c r="Q89" t="n">
-        <v>28.6</v>
+        <v>23.7</v>
       </c>
       <c r="R89" t="n">
-        <v>12.6</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -22794,7 +22790,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>36.3</v>
+        <v>62.1</v>
       </c>
       <c r="G90" t="n">
         <v>100</v>
@@ -22815,16 +22811,16 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>14.6</v>
+        <v>12.8</v>
       </c>
       <c r="P90" t="n">
-        <v>1.81</v>
+        <v>3.26</v>
       </c>
       <c r="Q90" t="n">
-        <v>23.7</v>
+        <v>28.6</v>
       </c>
       <c r="R90" t="n">
-        <v>27.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="91">
@@ -26746,12 +26742,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>長聖</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -26760,10 +26756,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.8</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -26808,12 +26804,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>長聖</t>
+          <t>欣高</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -26822,10 +26818,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>14.8</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -26839,12 +26835,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>浩鼎</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -26852,8 +26848,12 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>52</v>
+      </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
@@ -26866,12 +26866,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>尚凡*</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -26880,29 +26880,29 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.699999999999999</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>浩鼎</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -26910,30 +26910,26 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>97</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>尚凡*</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -26942,10 +26938,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -27238,12 +27234,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>欣陸</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -27252,17 +27248,17 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.3</v>
+        <v>20.5</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="F21" t="n">
         <v>13</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
@@ -27300,12 +27296,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>欣陸</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -27314,17 +27310,17 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20.5</v>
+        <v>10.3</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="F23" t="n">
         <v>13</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
@@ -27668,24 +27664,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>茂順</t>
+          <t>緯軟</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="E35" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F35" t="n">
         <v>27</v>
@@ -27699,24 +27695,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>緯軟</t>
+          <t>茂順</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="E36" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F36" t="n">
         <v>27</v>
@@ -27792,55 +27788,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>275</v>
+        <v>20.4</v>
       </c>
       <c r="E39" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="F39" t="n">
         <v>37</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>83.3</v>
+        <v>275</v>
       </c>
       <c r="E40" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F40" t="n">
         <v>37</v>
@@ -27854,31 +27850,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20.4</v>
+        <v>83.3</v>
       </c>
       <c r="E41" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F41" t="n">
         <v>37</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
@@ -28536,12 +28532,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -28550,10 +28546,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>75</v>
+        <v>19.9</v>
       </c>
       <c r="E63" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F63" t="n">
         <v>68</v>
@@ -28567,12 +28563,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -28581,10 +28577,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>19.9</v>
+        <v>75</v>
       </c>
       <c r="E64" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F64" t="n">
         <v>68</v>
@@ -28970,24 +28966,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>中工</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>21</v>
+        <v>27.2</v>
       </c>
       <c r="E77" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F77" t="n">
         <v>84</v>
@@ -29001,24 +28997,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>27.2</v>
+        <v>21</v>
       </c>
       <c r="E78" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F78" t="n">
         <v>84</v>
@@ -29156,62 +29152,62 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5637.5</v>
+        <v>16.9</v>
       </c>
       <c r="E83" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="F83" t="n">
         <v>88</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>16.9</v>
+        <v>5637.5</v>
       </c>
       <c r="E84" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="F84" t="n">
         <v>88</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
@@ -29311,12 +29307,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -29325,10 +29321,10 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>22.3</v>
+        <v>30.2</v>
       </c>
       <c r="E88" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F88" t="n">
         <v>91</v>
@@ -29342,12 +29338,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -29356,10 +29352,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>30.2</v>
+        <v>22.3</v>
       </c>
       <c r="E89" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F89" t="n">
         <v>91</v>
@@ -29373,62 +29369,62 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>新鉅科</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7.3</v>
+        <v>16</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F90" t="n">
         <v>92</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>新鉅科</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>16</v>
+        <v>7.3</v>
       </c>
       <c r="E91" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>92</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
@@ -29466,24 +29462,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>15.5</v>
+        <v>41.4</v>
       </c>
       <c r="E93" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F93" t="n">
         <v>94</v>
@@ -29497,24 +29493,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>41.4</v>
+        <v>15.5</v>
       </c>
       <c r="E94" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F94" t="n">
         <v>94</v>
@@ -29559,12 +29555,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -29573,10 +29569,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>19.8</v>
+        <v>46.4</v>
       </c>
       <c r="E96" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F96" t="n">
         <v>95</v>
@@ -29621,24 +29617,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>46.4</v>
+        <v>19.8</v>
       </c>
       <c r="E98" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F98" t="n">
         <v>95</v>
@@ -29869,12 +29865,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -29883,29 +29879,29 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>222.9</v>
+        <v>94.8</v>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="F106" t="n">
         <v>97</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -29914,17 +29910,17 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>94.8</v>
+        <v>222.9</v>
       </c>
       <c r="E107" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="F107" t="n">
         <v>97</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
@@ -29962,12 +29958,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -29976,17 +29972,17 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.5</v>
+        <v>310.9</v>
       </c>
       <c r="E109" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="F109" t="n">
         <v>98</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
@@ -30055,12 +30051,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -30069,17 +30065,17 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>30.3</v>
+        <v>10.5</v>
       </c>
       <c r="E112" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="F112" t="n">
         <v>98</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
@@ -30179,12 +30175,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -30193,10 +30189,10 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>310.9</v>
+        <v>30.3</v>
       </c>
       <c r="E116" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F116" t="n">
         <v>98</v>
@@ -30241,12 +30237,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -30255,7 +30251,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>476.9</v>
+        <v>3883.3</v>
       </c>
       <c r="E118" t="n">
         <v>100</v>
@@ -30303,12 +30299,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -30317,10 +30313,10 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>251.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E120" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F120" t="n">
         <v>99</v>
@@ -30396,12 +30392,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -30410,7 +30406,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3883.3</v>
+        <v>476.9</v>
       </c>
       <c r="E123" t="n">
         <v>100</v>
@@ -30427,12 +30423,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -30441,10 +30437,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>49.5</v>
+        <v>26</v>
       </c>
       <c r="E124" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F124" t="n">
         <v>99</v>
@@ -30458,12 +30454,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -30472,10 +30468,10 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>26</v>
+        <v>49.5</v>
       </c>
       <c r="E125" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="F125" t="n">
         <v>99</v>
@@ -30489,12 +30485,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -30503,7 +30499,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>72.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="E126" t="n">
         <v>98</v>
@@ -30551,12 +30547,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -30565,10 +30561,10 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>83.40000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="E128" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F128" t="n">
         <v>99</v>
@@ -30582,12 +30578,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -30596,10 +30592,10 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>45.8</v>
+        <v>72.7</v>
       </c>
       <c r="E129" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F129" t="n">
         <v>99</v>
@@ -30613,24 +30609,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>中再保</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>75.40000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="E130" t="n">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="F130" t="n">
         <v>99</v>
@@ -30644,24 +30640,24 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>中再保</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.7</v>
+        <v>251.2</v>
       </c>
       <c r="E131" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="F131" t="n">
         <v>99</v>
@@ -30768,12 +30764,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -30782,10 +30778,10 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>115.6</v>
+        <v>600</v>
       </c>
       <c r="E135" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F135" t="n">
         <v>100</v>
@@ -30861,12 +30857,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -30875,10 +30871,10 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>600</v>
+        <v>115.6</v>
       </c>
       <c r="E138" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F138" t="n">
         <v>100</v>
@@ -31109,12 +31105,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -31123,7 +31119,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>62.1</v>
+        <v>36.3</v>
       </c>
       <c r="E146" t="n">
         <v>100</v>
@@ -31140,12 +31136,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -31154,7 +31150,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>36.3</v>
+        <v>62.1</v>
       </c>
       <c r="E147" t="n">
         <v>100</v>
@@ -31264,12 +31260,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -31278,10 +31274,10 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>163.5</v>
+        <v>66.5</v>
       </c>
       <c r="E151" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F151" t="n">
         <v>100</v>
@@ -31295,12 +31291,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -31309,10 +31305,10 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>66.5</v>
+        <v>163.5</v>
       </c>
       <c r="E152" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F152" t="n">
         <v>100</v>
@@ -31388,12 +31384,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -31402,29 +31398,29 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>25.9</v>
+        <v>24.2</v>
       </c>
       <c r="E155" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="F155" t="n">
         <v>100</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -31433,17 +31429,17 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>24.2</v>
+        <v>45.2</v>
       </c>
       <c r="E156" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F156" t="n">
         <v>100</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
@@ -31512,12 +31508,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -31526,10 +31522,10 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>45.2</v>
+        <v>25.9</v>
       </c>
       <c r="E159" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F159" t="n">
         <v>100</v>
@@ -31605,21 +31601,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>正達</t>
+          <t>群益證</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+          <t>金融🏦</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>61</v>
+      </c>
       <c r="F162" t="n">
         <v>100</v>
       </c>
@@ -31663,12 +31663,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>正達</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -31676,61 +31676,57 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D164" t="n">
-        <v>308.3</v>
-      </c>
-      <c r="E164" t="n">
-        <v>3</v>
-      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>100</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>光環</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>17.3</v>
+        <v>308.3</v>
       </c>
       <c r="E165" t="n">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="F165" t="n">
         <v>100</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -31739,10 +31735,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="E166" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F166" t="n">
         <v>100</v>
@@ -31756,12 +31752,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -31770,10 +31766,10 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="E167" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F167" t="n">
         <v>100</v>
@@ -31787,12 +31783,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -31801,10 +31797,10 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>25.1</v>
+        <v>16</v>
       </c>
       <c r="E168" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="F168" t="n">
         <v>100</v>
@@ -31818,12 +31814,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>群益證</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -31832,10 +31828,10 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.1</v>
+        <v>17.3</v>
       </c>
       <c r="E169" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F169" t="n">
         <v>100</v>
@@ -31849,12 +31845,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -31863,10 +31859,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>16</v>
+        <v>25.1</v>
       </c>
       <c r="E170" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F170" t="n">
         <v>100</v>

--- a/data/未來PE報表.xlsx
+++ b/data/未來PE報表.xlsx
@@ -24,16 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,92 +424,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -16984,92 +16972,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -23066,92 +23054,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -23784,92 +23772,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -24432,92 +24420,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -24946,92 +24934,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -26610,37 +26598,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -31950,12 +31938,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>值</t>
         </is>

--- a/data/未來PE報表.xlsx
+++ b/data/未來PE報表.xlsx
@@ -24,13 +24,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,92 +436,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -16474,12 +16486,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>國票金</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16494,10 +16506,10 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>16.8</v>
+        <v>23.9</v>
       </c>
       <c r="G266" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
@@ -16506,7 +16518,7 @@
       <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -16519,21 +16531,21 @@
       </c>
       <c r="P266" t="inlineStr"/>
       <c r="Q266" t="n">
-        <v>117.9</v>
+        <v>147.9</v>
       </c>
       <c r="R266" t="n">
-        <v>37.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16548,10 +16560,10 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>17.3</v>
+        <v>19.8</v>
       </c>
       <c r="G267" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
@@ -16573,21 +16585,21 @@
       </c>
       <c r="P267" t="inlineStr"/>
       <c r="Q267" t="n">
-        <v>76.09999999999999</v>
+        <v>22.3</v>
       </c>
       <c r="R267" t="n">
-        <v>20.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16602,10 +16614,10 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>25.1</v>
+        <v>16.8</v>
       </c>
       <c r="G268" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
@@ -16627,21 +16639,21 @@
       </c>
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="n">
-        <v>227.3</v>
+        <v>117.9</v>
       </c>
       <c r="R268" t="n">
-        <v>14.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16656,10 +16668,10 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>16</v>
+        <v>25.1</v>
       </c>
       <c r="G269" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
@@ -16681,21 +16693,21 @@
       </c>
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="n">
-        <v>28.8</v>
+        <v>227.3</v>
       </c>
       <c r="R269" t="n">
-        <v>47.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16710,10 +16722,10 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>19.8</v>
+        <v>17.4</v>
       </c>
       <c r="G270" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
@@ -16735,21 +16747,21 @@
       </c>
       <c r="P270" t="inlineStr"/>
       <c r="Q270" t="n">
-        <v>22.3</v>
+        <v>-172.7</v>
       </c>
       <c r="R270" t="n">
-        <v>-0.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16764,10 +16776,10 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>23.9</v>
+        <v>16.6</v>
       </c>
       <c r="G271" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
@@ -16776,7 +16788,7 @@
       <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -16789,21 +16801,21 @@
       </c>
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="n">
-        <v>147.9</v>
+        <v>-300.3</v>
       </c>
       <c r="R271" t="n">
-        <v>4.2</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -16818,10 +16830,10 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="G272" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
@@ -16830,7 +16842,7 @@
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -16843,21 +16855,21 @@
       </c>
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="n">
-        <v>24.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R272" t="n">
-        <v>22.6</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -16872,10 +16884,10 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="G273" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
@@ -16884,7 +16896,7 @@
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -16897,21 +16909,21 @@
       </c>
       <c r="P273" t="inlineStr"/>
       <c r="Q273" t="n">
-        <v>-300.3</v>
+        <v>24.8</v>
       </c>
       <c r="R273" t="n">
-        <v>32.1</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16926,10 +16938,10 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="G274" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
@@ -16951,10 +16963,10 @@
       </c>
       <c r="P274" t="inlineStr"/>
       <c r="Q274" t="n">
-        <v>-172.7</v>
+        <v>28.8</v>
       </c>
       <c r="R274" t="n">
-        <v>24.1</v>
+        <v>47.6</v>
       </c>
     </row>
   </sheetData>
@@ -16972,92 +16984,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -23054,92 +23066,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -23772,92 +23784,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -24420,92 +24432,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -24934,92 +24946,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>四象限</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
@@ -26598,37 +26610,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -31709,12 +31721,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -31723,10 +31735,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="E166" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F166" t="n">
         <v>100</v>
@@ -31740,12 +31752,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -31754,10 +31766,10 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>16.8</v>
+        <v>25.1</v>
       </c>
       <c r="E167" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F167" t="n">
         <v>100</v>
@@ -31771,12 +31783,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -31785,10 +31797,10 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E168" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F168" t="n">
         <v>100</v>
@@ -31833,12 +31845,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -31847,10 +31859,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>25.1</v>
+        <v>16.6</v>
       </c>
       <c r="E170" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F170" t="n">
         <v>100</v>
@@ -31864,12 +31876,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -31878,10 +31890,10 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>16.6</v>
+        <v>17.3</v>
       </c>
       <c r="E171" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F171" t="n">
         <v>100</v>
@@ -31895,12 +31907,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -31909,10 +31921,10 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E172" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F172" t="n">
         <v>100</v>
@@ -31938,12 +31950,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>

--- a/data/未來PE報表.xlsx
+++ b/data/未來PE報表.xlsx
@@ -16486,12 +16486,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16506,10 +16506,10 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>23.9</v>
+        <v>16.8</v>
       </c>
       <c r="G266" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
@@ -16518,7 +16518,7 @@
       <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -16531,21 +16531,21 @@
       </c>
       <c r="P266" t="inlineStr"/>
       <c r="Q266" t="n">
-        <v>147.9</v>
+        <v>117.9</v>
       </c>
       <c r="R266" t="n">
-        <v>4.2</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16560,10 +16560,10 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>19.8</v>
+        <v>17.3</v>
       </c>
       <c r="G267" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
@@ -16585,21 +16585,21 @@
       </c>
       <c r="P267" t="inlineStr"/>
       <c r="Q267" t="n">
-        <v>22.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R267" t="n">
-        <v>-0.2</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16614,10 +16614,10 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>16.8</v>
+        <v>25.1</v>
       </c>
       <c r="G268" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
@@ -16639,21 +16639,21 @@
       </c>
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="n">
-        <v>117.9</v>
+        <v>227.3</v>
       </c>
       <c r="R268" t="n">
-        <v>37.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>25.1</v>
+        <v>16</v>
       </c>
       <c r="G269" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
@@ -16693,21 +16693,21 @@
       </c>
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="n">
-        <v>227.3</v>
+        <v>28.8</v>
       </c>
       <c r="R269" t="n">
-        <v>14.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16722,10 +16722,10 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>17.4</v>
+        <v>19.8</v>
       </c>
       <c r="G270" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
@@ -16747,21 +16747,21 @@
       </c>
       <c r="P270" t="inlineStr"/>
       <c r="Q270" t="n">
-        <v>-172.7</v>
+        <v>22.3</v>
       </c>
       <c r="R270" t="n">
-        <v>24.1</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>國票金</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16776,10 +16776,10 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>16.6</v>
+        <v>23.9</v>
       </c>
       <c r="G271" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
@@ -16788,7 +16788,7 @@
       <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -16801,21 +16801,21 @@
       </c>
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="n">
-        <v>-300.3</v>
+        <v>147.9</v>
       </c>
       <c r="R271" t="n">
-        <v>32.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -16830,10 +16830,10 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="G272" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
@@ -16842,7 +16842,7 @@
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -16855,21 +16855,21 @@
       </c>
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="n">
-        <v>76.09999999999999</v>
+        <v>24.8</v>
       </c>
       <c r="R272" t="n">
-        <v>20.3</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -16884,10 +16884,10 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="G273" t="n">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
@@ -16896,7 +16896,7 @@
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -16909,21 +16909,21 @@
       </c>
       <c r="P273" t="inlineStr"/>
       <c r="Q273" t="n">
-        <v>24.8</v>
+        <v>-300.3</v>
       </c>
       <c r="R273" t="n">
-        <v>22.6</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16938,10 +16938,10 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="G274" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
@@ -16963,10 +16963,10 @@
       </c>
       <c r="P274" t="inlineStr"/>
       <c r="Q274" t="n">
-        <v>28.8</v>
+        <v>-172.7</v>
       </c>
       <c r="R274" t="n">
-        <v>47.6</v>
+        <v>24.1</v>
       </c>
     </row>
   </sheetData>
@@ -31721,12 +31721,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -31735,10 +31735,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="E166" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F166" t="n">
         <v>100</v>
@@ -31752,12 +31752,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -31766,10 +31766,10 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>25.1</v>
+        <v>16.8</v>
       </c>
       <c r="E167" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F167" t="n">
         <v>100</v>
@@ -31783,12 +31783,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -31797,10 +31797,10 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E168" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F168" t="n">
         <v>100</v>
@@ -31845,12 +31845,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -31859,10 +31859,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>16.6</v>
+        <v>25.1</v>
       </c>
       <c r="E170" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F170" t="n">
         <v>100</v>
@@ -31876,12 +31876,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -31890,10 +31890,10 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>17.3</v>
+        <v>16.6</v>
       </c>
       <c r="E171" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F171" t="n">
         <v>100</v>
@@ -31907,12 +31907,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -31921,10 +31921,10 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E172" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F172" t="n">
         <v>100</v>
